--- a/data/trans_orig/PCS12_SP_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114936</t>
+          <t>115165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153710</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103525</t>
+          <t>103895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146054</t>
+          <t>143824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228625</t>
+          <t>230863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>289681</t>
+          <t>285772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237686</t>
+          <t>236871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289513</t>
+          <t>287370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149529</t>
+          <t>148027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>191526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>395100</t>
+          <t>398887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467796</t>
+          <t>467356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>156750</t>
+          <t>157181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201716</t>
+          <t>201786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>188039</t>
+          <t>185318</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234266</t>
+          <t>234630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>353705</t>
+          <t>351580</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>418421</t>
+          <t>419633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>100063</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141063</t>
+          <t>139827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>166084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209516</t>
+          <t>212524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>275894</t>
+          <t>279384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337643</t>
+          <t>338723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230584</t>
+          <t>230757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>290841</t>
+          <t>287778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>150767</t>
+          <t>149553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>197687</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>396279</t>
+          <t>395751</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>471335</t>
+          <t>467812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>281866</t>
+          <t>284829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>345666</t>
+          <t>345214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>29,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>211650</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>186736</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>236745</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>527102</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>484005</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>565827</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>25,08%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>29,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>211650</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>187368</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>237656</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>24,54%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>527102</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>482598</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>566300</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224597</t>
+          <t>223681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279771</t>
+          <t>280158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>288198</t>
+          <t>286083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347514</t>
+          <t>349788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534487</t>
+          <t>529611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612427</t>
+          <t>609322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159545</t>
+          <t>159792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238067</t>
+          <t>238487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>294711</t>
+          <t>296849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>367627</t>
+          <t>367820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>440241</t>
+          <t>440146</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148932</t>
+          <t>149241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194079</t>
+          <t>194388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131512</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173740</t>
+          <t>174445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289687</t>
+          <t>294233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>356185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165250</t>
+          <t>166537</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>214175</t>
+          <t>213037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119443</t>
+          <t>119456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162060</t>
+          <t>161696</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>297702</t>
+          <t>297834</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360945</t>
+          <t>361621</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178027</t>
+          <t>176631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>225852</t>
+          <t>226421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171329</t>
+          <t>173141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218620</t>
+          <t>220291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364834</t>
+          <t>364188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>431462</t>
+          <t>428630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98281</t>
+          <t>98367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137105</t>
+          <t>138471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175589</t>
+          <t>175794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>219890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282969</t>
+          <t>282166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344565</t>
+          <t>342663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>215272</t>
+          <t>211879</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>265653</t>
+          <t>266303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>205606</t>
+          <t>203403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>257440</t>
+          <t>259352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>430837</t>
+          <t>434231</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>505302</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274736</t>
+          <t>272025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328380</t>
+          <t>325662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214476</t>
+          <t>219014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271452</t>
+          <t>272165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>505375</t>
+          <t>502081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584167</t>
+          <t>581481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>230724</t>
+          <t>232312</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>284062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>259956</t>
+          <t>265241</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>322268</t>
+          <t>323390</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>515620</t>
+          <t>516874</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>594200</t>
+          <t>593770</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124841</t>
+          <t>125288</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165887</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243847</t>
+          <t>243391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298938</t>
+          <t>302150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378861</t>
+          <t>380790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>448421</t>
+          <t>451270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>749427</t>
+          <t>750304</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>850486</t>
+          <t>848608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>632651</t>
+          <t>633440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>722382</t>
+          <t>722978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1407531</t>
+          <t>1410103</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1545783</t>
+          <t>1548560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1013663</t>
+          <t>1011915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1120740</t>
+          <t>1121842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>720642</t>
+          <t>717740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>819468</t>
+          <t>812969</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1760659</t>
+          <t>1757840</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1908415</t>
+          <t>1907379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>843275</t>
+          <t>842215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>945505</t>
+          <t>946530</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>961833</t>
+          <t>958919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1068566</t>
+          <t>1070628</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1826442</t>
+          <t>1833389</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1982955</t>
+          <t>1981908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>479996</t>
+          <t>474454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>560644</t>
+          <t>560810</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>865860</t>
+          <t>868738</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>971428</t>
+          <t>973390</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1365870</t>
+          <t>1362956</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1505658</t>
+          <t>1504916</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>184473</t>
+          <t>181571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233222</t>
+          <t>233620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140407</t>
+          <t>141397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184375</t>
+          <t>185486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,47 +3860,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>370387</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>339203</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>405130</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>26,45%</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>370387</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>335419</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>404015</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148216</t>
+          <t>150394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195099</t>
+          <t>196230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139924</t>
+          <t>137639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>186280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303290</t>
+          <t>301973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365531</t>
+          <t>366959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162716</t>
+          <t>165463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>213675</t>
+          <t>212673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132258</t>
+          <t>132134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>177044</t>
+          <t>176908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311636</t>
+          <t>310186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>381089</t>
+          <t>375912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114343</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155413</t>
+          <t>157389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193353</t>
+          <t>193264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243429</t>
+          <t>241667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320198</t>
+          <t>319734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387329</t>
+          <t>383544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>263041</t>
+          <t>263254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323908</t>
+          <t>323092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>202548</t>
+          <t>202542</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260704</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>479224</t>
+          <t>483855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>560495</t>
+          <t>564506</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238925</t>
+          <t>242872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300904</t>
+          <t>300003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202093</t>
+          <t>201056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256606</t>
+          <t>257140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>461793</t>
+          <t>462788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542203</t>
+          <t>542822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234815</t>
+          <t>237117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294196</t>
+          <t>293598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239822</t>
+          <t>241985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298066</t>
+          <t>299030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489103</t>
+          <t>494216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576577</t>
+          <t>572629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165793</t>
+          <t>164691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217689</t>
+          <t>215250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>279426</t>
+          <t>277496</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335656</t>
+          <t>338333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>456625</t>
+          <t>457801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>538944</t>
+          <t>536202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192163</t>
+          <t>192691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>241866</t>
+          <t>245813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142321</t>
+          <t>141290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>189416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347063</t>
+          <t>346978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>420440</t>
+          <t>417312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204826</t>
+          <t>204501</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257725</t>
+          <t>258532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>174832</t>
+          <t>176819</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227676</t>
+          <t>226277</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>395271</t>
+          <t>398822</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>466264</t>
+          <t>468845</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180043</t>
+          <t>176477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230732</t>
+          <t>228269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179157</t>
+          <t>180866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234066</t>
+          <t>235102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375021</t>
+          <t>373578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>450158</t>
+          <t>450365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87776</t>
+          <t>89207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176979</t>
+          <t>178673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230203</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276143</t>
+          <t>275715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341874</t>
+          <t>342770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>235232</t>
+          <t>233679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>293372</t>
+          <t>291047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203713</t>
+          <t>199628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>255827</t>
+          <t>255390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>451637</t>
+          <t>454202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>532906</t>
+          <t>528923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221433</t>
+          <t>220777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278557</t>
+          <t>273488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214808</t>
+          <t>213778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268574</t>
+          <t>268208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>450747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527535</t>
+          <t>526430</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>227780</t>
+          <t>227426</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282160</t>
+          <t>283580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>247842</t>
+          <t>244385</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>304542</t>
+          <t>301906</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>488373</t>
+          <t>491852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>572942</t>
+          <t>571540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158297</t>
+          <t>157260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207779</t>
+          <t>209473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280495</t>
+          <t>281547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>340443</t>
+          <t>344000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>455306</t>
+          <t>449055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>534213</t>
+          <t>530738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>925812</t>
+          <t>928346</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1030545</t>
+          <t>1036728</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>736054</t>
+          <t>731139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>840223</t>
+          <t>836065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1689052</t>
+          <t>1688530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1834196</t>
+          <t>1838137</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>870564</t>
+          <t>875537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>981067</t>
+          <t>980566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>781802</t>
+          <t>780560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>882955</t>
+          <t>883560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1676748</t>
+          <t>1678579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1820548</t>
+          <t>1828078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>855098</t>
+          <t>862228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>968666</t>
+          <t>970970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>852401</t>
+          <t>854639</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>958892</t>
+          <t>960953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1741595</t>
+          <t>1732361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1895029</t>
+          <t>1895596</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>573040</t>
+          <t>569321</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>658524</t>
+          <t>661015</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>980169</t>
+          <t>978146</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1088966</t>
+          <t>1093802</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1579453</t>
+          <t>1581308</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1724670</t>
+          <t>1725508</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>238314</t>
+          <t>241096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289443</t>
+          <t>291735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178966</t>
+          <t>177663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223833</t>
+          <t>224386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>429102</t>
+          <t>430621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>498013</t>
+          <t>499923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96499</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135160</t>
+          <t>136628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103509</t>
+          <t>101839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143105</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209158</t>
+          <t>208607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265822</t>
+          <t>264240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143098</t>
+          <t>143234</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>187396</t>
+          <t>190197</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126937</t>
+          <t>126965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170262</t>
+          <t>170647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281803</t>
+          <t>283750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>345598</t>
+          <t>345257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110565</t>
+          <t>109550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150924</t>
+          <t>150010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178563</t>
+          <t>178870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>227295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300691</t>
+          <t>302991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364661</t>
+          <t>364135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>320042</t>
+          <t>319753</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>381776</t>
+          <t>382891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>278043</t>
+          <t>278608</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>337647</t>
+          <t>336220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>615606</t>
+          <t>615225</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>699783</t>
+          <t>701053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256587</t>
+          <t>259000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>316328</t>
+          <t>316692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201275</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255677</t>
+          <t>255220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>477928</t>
+          <t>474195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>554595</t>
+          <t>551935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192306</t>
+          <t>193902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250085</t>
+          <t>248236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204973</t>
+          <t>205202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257125</t>
+          <t>258372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412407</t>
+          <t>412009</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491642</t>
+          <t>492734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145064</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191568</t>
+          <t>190585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246281</t>
+          <t>247714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>305267</t>
+          <t>305952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>404420</t>
+          <t>404782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>481274</t>
+          <t>483879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239127</t>
+          <t>239878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295711</t>
+          <t>297163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>203962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>253209</t>
+          <t>253765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>456879</t>
+          <t>459044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>532725</t>
+          <t>532171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>152739</t>
+          <t>154773</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>204717</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146684</t>
+          <t>146982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190825</t>
+          <t>193087</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315333</t>
+          <t>308857</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>378343</t>
+          <t>378249</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177553</t>
+          <t>177256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230799</t>
+          <t>229383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181927</t>
+          <t>181180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233908</t>
+          <t>232673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375308</t>
+          <t>378744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446528</t>
+          <t>447146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92026</t>
+          <t>93656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132331</t>
+          <t>133094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157742</t>
+          <t>158724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206836</t>
+          <t>208958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261439</t>
+          <t>262957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328349</t>
+          <t>327242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>306047</t>
+          <t>302521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>367101</t>
+          <t>362659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>286040</t>
+          <t>285223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>346316</t>
+          <t>346540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>608751</t>
+          <t>603434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>693065</t>
+          <t>691079</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223584</t>
+          <t>222427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277082</t>
+          <t>276547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219309</t>
+          <t>219015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275113</t>
+          <t>274306</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456901</t>
+          <t>457707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534588</t>
+          <t>532486</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170918</t>
+          <t>172650</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>221797</t>
+          <t>222642</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>190094</t>
+          <t>189786</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>245439</t>
+          <t>242578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>377542</t>
+          <t>377612</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>452753</t>
+          <t>454285</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137276</t>
+          <t>134770</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183979</t>
+          <t>182187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235940</t>
+          <t>235677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294993</t>
+          <t>295766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388456</t>
+          <t>389981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463191</t>
+          <t>464743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1164514</t>
+          <t>1154983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1271324</t>
+          <t>1270856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1000228</t>
+          <t>990064</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1109505</t>
+          <t>1100555</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2193811</t>
+          <t>2181053</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2345257</t>
+          <t>2346156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>775342</t>
+          <t>776741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>878370</t>
+          <t>879317</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>718749</t>
+          <t>718801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>817955</t>
+          <t>817800</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1527824</t>
+          <t>1527876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1663821</t>
+          <t>1667342</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>734945</t>
+          <t>730079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>837716</t>
+          <t>833278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>749725</t>
+          <t>756507</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>849623</t>
+          <t>856043</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1510292</t>
+          <t>1513034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1656085</t>
+          <t>1662086</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>523746</t>
+          <t>525968</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>609668</t>
+          <t>616499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>874369</t>
+          <t>875309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>984036</t>
+          <t>985535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1419595</t>
+          <t>1422095</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1563796</t>
+          <t>1562434</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109259</t>
+          <t>108778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>164702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107494</t>
+          <t>107531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143345</t>
+          <t>143015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229772</t>
+          <t>226672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291711</t>
+          <t>294532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155171</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201427</t>
+          <t>200419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162499</t>
+          <t>159934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199328</t>
+          <t>198057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>326123</t>
+          <t>324996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387647</t>
+          <t>383670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>127007</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175975</t>
+          <t>174689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133869</t>
+          <t>132925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168439</t>
+          <t>169617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272484</t>
+          <t>271990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>330454</t>
+          <t>331029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149746</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191898</t>
+          <t>191841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199655</t>
+          <t>198649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235497</t>
+          <t>236863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>358551</t>
+          <t>356906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>419912</t>
+          <t>415306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148063</t>
+          <t>135830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361027</t>
+          <t>359556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205693</t>
+          <t>205143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>250698</t>
+          <t>253876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346094</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>582443</t>
+          <t>585083</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169920</t>
+          <t>172097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415479</t>
+          <t>411981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220710</t>
+          <t>219945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267780</t>
+          <t>269789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365828</t>
+          <t>366384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>647323</t>
+          <t>648604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93956</t>
+          <t>93743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>233900</t>
+          <t>237298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175427</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217891</t>
+          <t>216224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250823</t>
+          <t>246505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>436676</t>
+          <t>439390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208637</t>
+          <t>208615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>775867</t>
+          <t>771009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>264318</t>
+          <t>262950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>308668</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>509243</t>
+          <t>506662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1144651</t>
+          <t>1194189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166084</t>
+          <t>166696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226947</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95484</t>
+          <t>97190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>275063</t>
+          <t>272270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256303</t>
+          <t>252891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>477739</t>
+          <t>474449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169350</t>
+          <t>165396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222087</t>
+          <t>220234</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87833</t>
+          <t>86146</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227201</t>
+          <t>227608</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>239584</t>
+          <t>220099</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>430946</t>
+          <t>431209</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>145024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191834</t>
+          <t>193744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>215523</t>
+          <t>217530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>625370</t>
+          <t>641444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378877</t>
+          <t>382110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>934624</t>
+          <t>944009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>126983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169626</t>
+          <t>169025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103212</t>
+          <t>101982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253933</t>
+          <t>251423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220789</t>
+          <t>215880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393452</t>
+          <t>392223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>165997</t>
+          <t>168834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>226372</t>
+          <t>227263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167775</t>
+          <t>170882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244182</t>
+          <t>244891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,47 +11721,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>22,48%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>409296</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>355904</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>451067</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>22,42%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>409296</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>352049</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>452110</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211716</t>
+          <t>213457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270016</t>
+          <t>268810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231659</t>
+          <t>230254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>441297</t>
+          <t>461617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466159</t>
+          <t>467124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>732261</t>
+          <t>719427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>257334</t>
+          <t>258290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>319011</t>
+          <t>320102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>201217</t>
+          <t>198171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>277691</t>
+          <t>276194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>478115</t>
+          <t>472207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>585162</t>
+          <t>584240</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177770</t>
+          <t>174624</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224588</t>
+          <t>224364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>268013</t>
+          <t>270758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368065</t>
+          <t>370080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>468274</t>
+          <t>466604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>576518</t>
+          <t>574401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -12235,17 +12235,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>797771</t>
+          <t>797772</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>609304</t>
+          <t>619679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>883045</t>
+          <t>884337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>616802</t>
+          <t>619932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>851607</t>
+          <t>854698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1359880</t>
+          <t>1358939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1697490</t>
+          <t>1694794</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>711976</t>
+          <t>720820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1026015</t>
+          <t>1016243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>749437</t>
+          <t>751071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1026163</t>
+          <t>1044637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1573823</t>
+          <t>1569734</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1990299</t>
+          <t>1987222</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>608486</t>
+          <t>626681</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>871127</t>
+          <t>870604</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799895</t>
+          <t>798814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1469142</t>
+          <t>1455734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1547472</t>
+          <t>1559234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2228221</t>
+          <t>2316422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>727315</t>
+          <t>726198</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1613373</t>
+          <t>1480569</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>858752</t>
+          <t>833870</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1118072</t>
+          <t>1116157</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1713593</t>
+          <t>1721211</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2514992</t>
+          <t>2611019</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115165</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155875</t>
+          <t>157706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103895</t>
+          <t>102616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143824</t>
+          <t>142632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230863</t>
+          <t>226070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285772</t>
+          <t>288863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236871</t>
+          <t>236503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287370</t>
+          <t>288860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>149980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191526</t>
+          <t>194176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>398887</t>
+          <t>398765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467356</t>
+          <t>464943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157181</t>
+          <t>158128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201786</t>
+          <t>202466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>185318</t>
+          <t>185616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234630</t>
+          <t>233069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>351580</t>
+          <t>353972</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>419633</t>
+          <t>419107</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100063</t>
+          <t>100251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139827</t>
+          <t>138986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166084</t>
+          <t>165809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212524</t>
+          <t>211129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279384</t>
+          <t>274102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>338723</t>
+          <t>336706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230757</t>
+          <t>230765</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>287778</t>
+          <t>286962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149553</t>
+          <t>149332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>196564</t>
+          <t>198700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>395751</t>
+          <t>393679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>467812</t>
+          <t>467460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284829</t>
+          <t>286922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>345214</t>
+          <t>348225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186736</t>
+          <t>185096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>236745</t>
+          <t>239354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484005</t>
+          <t>486653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>565827</t>
+          <t>565001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>223681</t>
+          <t>224303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280158</t>
+          <t>280525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286083</t>
+          <t>290123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349788</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529611</t>
+          <t>531109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609322</t>
+          <t>610714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116707</t>
+          <t>113582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159792</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238487</t>
+          <t>235792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>296849</t>
+          <t>291770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>367820</t>
+          <t>368070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>440146</t>
+          <t>441499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149241</t>
+          <t>149891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194388</t>
+          <t>195678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129796</t>
+          <t>132420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174445</t>
+          <t>175874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294233</t>
+          <t>291522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356185</t>
+          <t>354055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166537</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>213037</t>
+          <t>214875</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119456</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161696</t>
+          <t>162903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>297834</t>
+          <t>297773</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>361621</t>
+          <t>362602</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176631</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226421</t>
+          <t>227101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173141</t>
+          <t>174252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220291</t>
+          <t>218506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364188</t>
+          <t>365729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>428630</t>
+          <t>429582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98367</t>
+          <t>97707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138471</t>
+          <t>136916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175794</t>
+          <t>172460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219890</t>
+          <t>220333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282166</t>
+          <t>281438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342663</t>
+          <t>344494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211879</t>
+          <t>213943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>266303</t>
+          <t>267192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203403</t>
+          <t>205550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259352</t>
+          <t>260820</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>434231</t>
+          <t>434312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>511918</t>
+          <t>510141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272025</t>
+          <t>273171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325662</t>
+          <t>327748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219014</t>
+          <t>217132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272165</t>
+          <t>273541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502081</t>
+          <t>508155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>581481</t>
+          <t>584138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>232312</t>
+          <t>236962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>284062</t>
+          <t>288710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>265241</t>
+          <t>260038</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>323390</t>
+          <t>319050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>516874</t>
+          <t>514795</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>593770</t>
+          <t>594065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125288</t>
+          <t>122703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>165835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243391</t>
+          <t>242994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302150</t>
+          <t>299325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380790</t>
+          <t>379296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>451270</t>
+          <t>451987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>750304</t>
+          <t>756304</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>848608</t>
+          <t>854936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>633440</t>
+          <t>634319</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>722978</t>
+          <t>727658</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1410103</t>
+          <t>1410090</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1548560</t>
+          <t>1547192</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1011915</t>
+          <t>1013832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1121842</t>
+          <t>1121247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>717740</t>
+          <t>718870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>812969</t>
+          <t>816034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1757840</t>
+          <t>1759492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1907379</t>
+          <t>1902877</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>842215</t>
+          <t>841794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>946530</t>
+          <t>941956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>958919</t>
+          <t>961497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1070628</t>
+          <t>1067850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1833389</t>
+          <t>1831455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1981908</t>
+          <t>1985114</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>474454</t>
+          <t>481030</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>560810</t>
+          <t>562924</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>868738</t>
+          <t>869194</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>973390</t>
+          <t>978300</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1362956</t>
+          <t>1371871</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1504916</t>
+          <t>1505426</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181571</t>
+          <t>183494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233620</t>
+          <t>232805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141397</t>
+          <t>141619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185486</t>
+          <t>187568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>339203</t>
+          <t>337144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>405130</t>
+          <t>400521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150394</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196230</t>
+          <t>198329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137639</t>
+          <t>141024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186280</t>
+          <t>183647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301973</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366959</t>
+          <t>368691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165463</t>
+          <t>165301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>212673</t>
+          <t>213432</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132134</t>
+          <t>132765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176908</t>
+          <t>178910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>310186</t>
+          <t>314627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>375912</t>
+          <t>378807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114301</t>
+          <t>115499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157389</t>
+          <t>156193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193264</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241667</t>
+          <t>240873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319734</t>
+          <t>318853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383544</t>
+          <t>385238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>263254</t>
+          <t>261438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323092</t>
+          <t>321825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>203781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258650</t>
+          <t>258767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>483855</t>
+          <t>482055</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>564506</t>
+          <t>564934</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>242872</t>
+          <t>243134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300003</t>
+          <t>301600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201056</t>
+          <t>201380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257140</t>
+          <t>258988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462788</t>
+          <t>459734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542822</t>
+          <t>542052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237117</t>
+          <t>236601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293598</t>
+          <t>295062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241985</t>
+          <t>237416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299030</t>
+          <t>296460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494216</t>
+          <t>492260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>572629</t>
+          <t>582121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164691</t>
+          <t>163614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215250</t>
+          <t>214358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>277496</t>
+          <t>276863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>338333</t>
+          <t>339456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>457801</t>
+          <t>451524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>536202</t>
+          <t>534393</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192691</t>
+          <t>189511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245813</t>
+          <t>242964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141290</t>
+          <t>143342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189416</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346978</t>
+          <t>346151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417312</t>
+          <t>418867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204501</t>
+          <t>202097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>258532</t>
+          <t>256769</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>176819</t>
+          <t>174994</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>226277</t>
+          <t>227463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>398822</t>
+          <t>395378</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>468845</t>
+          <t>469745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176477</t>
+          <t>177498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228269</t>
+          <t>231376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180866</t>
+          <t>178455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235102</t>
+          <t>234068</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373578</t>
+          <t>372936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>450365</t>
+          <t>448390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89207</t>
+          <t>88659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130850</t>
+          <t>130778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>178162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>228240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275715</t>
+          <t>276317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342770</t>
+          <t>342856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>233679</t>
+          <t>235915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>291047</t>
+          <t>294140</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199628</t>
+          <t>200005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>255182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>454202</t>
+          <t>448736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>528923</t>
+          <t>532009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220777</t>
+          <t>218881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273488</t>
+          <t>273454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213778</t>
+          <t>211781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268208</t>
+          <t>266950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450747</t>
+          <t>450392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526430</t>
+          <t>528460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>227426</t>
+          <t>228325</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>283580</t>
+          <t>289217</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>244385</t>
+          <t>245426</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>301906</t>
+          <t>304961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>491852</t>
+          <t>489037</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>571540</t>
+          <t>576494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>157260</t>
+          <t>158357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209473</t>
+          <t>210117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>281547</t>
+          <t>280915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>344000</t>
+          <t>343365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>449055</t>
+          <t>451125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>530738</t>
+          <t>532131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>928346</t>
+          <t>922885</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1036728</t>
+          <t>1031728</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>731139</t>
+          <t>736181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>836065</t>
+          <t>834763</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1688530</t>
+          <t>1691758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1838137</t>
+          <t>1838828</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>875537</t>
+          <t>867555</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>980566</t>
+          <t>981541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>780560</t>
+          <t>781847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>883560</t>
+          <t>886307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1678579</t>
+          <t>1678606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1828078</t>
+          <t>1824118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>862228</t>
+          <t>864215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>970970</t>
+          <t>967440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>854639</t>
+          <t>853788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>960953</t>
+          <t>957168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1732361</t>
+          <t>1747682</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1895596</t>
+          <t>1894215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>569321</t>
+          <t>563457</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>661015</t>
+          <t>658834</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>978146</t>
+          <t>978744</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1093802</t>
+          <t>1093225</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1581308</t>
+          <t>1581783</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1725508</t>
+          <t>1722356</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241096</t>
+          <t>240924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>291735</t>
+          <t>291342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177663</t>
+          <t>179484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>226176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>430621</t>
+          <t>428587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>499923</t>
+          <t>499080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136628</t>
+          <t>136528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101839</t>
+          <t>102765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142142</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208607</t>
+          <t>209774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>264240</t>
+          <t>264767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143234</t>
+          <t>142933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>190197</t>
+          <t>187496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126965</t>
+          <t>128483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170647</t>
+          <t>170121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283750</t>
+          <t>280035</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>345257</t>
+          <t>344163</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109550</t>
+          <t>108901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150010</t>
+          <t>149257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178870</t>
+          <t>176547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227295</t>
+          <t>227569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302991</t>
+          <t>302315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364135</t>
+          <t>367656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>319753</t>
+          <t>317831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>382891</t>
+          <t>378742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>278608</t>
+          <t>278727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>336220</t>
+          <t>337965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>615225</t>
+          <t>612679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>701053</t>
+          <t>697115</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259000</t>
+          <t>253862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>316692</t>
+          <t>314761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200044</t>
+          <t>203821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255220</t>
+          <t>257775</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474195</t>
+          <t>475462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>551935</t>
+          <t>552789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>193902</t>
+          <t>190346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>248236</t>
+          <t>246011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205202</t>
+          <t>204031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258372</t>
+          <t>256981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412009</t>
+          <t>415244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>492734</t>
+          <t>495187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>143128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190585</t>
+          <t>194074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>247714</t>
+          <t>245037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>305952</t>
+          <t>302099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>404782</t>
+          <t>409163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>483879</t>
+          <t>484121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239878</t>
+          <t>240635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297163</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203962</t>
+          <t>202389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>253765</t>
+          <t>253263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459044</t>
+          <t>461463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>532171</t>
+          <t>532326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154773</t>
+          <t>154701</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204717</t>
+          <t>203812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146982</t>
+          <t>146200</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>193087</t>
+          <t>192007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>308857</t>
+          <t>313378</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>378249</t>
+          <t>377651</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177256</t>
+          <t>177348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229383</t>
+          <t>226194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181180</t>
+          <t>181592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232673</t>
+          <t>232559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378744</t>
+          <t>372443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>447146</t>
+          <t>445148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93656</t>
+          <t>93928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133094</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>159248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208958</t>
+          <t>208170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262957</t>
+          <t>262565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327242</t>
+          <t>326673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>302521</t>
+          <t>304244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>362659</t>
+          <t>359976</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285223</t>
+          <t>284203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>346540</t>
+          <t>345012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>603434</t>
+          <t>606694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>691079</t>
+          <t>689178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222427</t>
+          <t>224839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276547</t>
+          <t>277030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219015</t>
+          <t>219273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274306</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457707</t>
+          <t>458083</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532486</t>
+          <t>534501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>172650</t>
+          <t>173793</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>222642</t>
+          <t>226012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>189786</t>
+          <t>192061</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>242578</t>
+          <t>242240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>377612</t>
+          <t>376573</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>454285</t>
+          <t>445688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134770</t>
+          <t>134846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182187</t>
+          <t>182004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235677</t>
+          <t>235837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295766</t>
+          <t>295249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>389981</t>
+          <t>386377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464743</t>
+          <t>465080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1154983</t>
+          <t>1160747</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1270856</t>
+          <t>1273627</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>990064</t>
+          <t>998562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1100555</t>
+          <t>1107849</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2181053</t>
+          <t>2188434</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2346156</t>
+          <t>2346876</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>776741</t>
+          <t>778186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>879317</t>
+          <t>879157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>718801</t>
+          <t>720603</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>817800</t>
+          <t>817759</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1527876</t>
+          <t>1524201</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1667342</t>
+          <t>1664535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>730079</t>
+          <t>735570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>833278</t>
+          <t>837914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756507</t>
+          <t>749385</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>856043</t>
+          <t>855968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1513034</t>
+          <t>1519542</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1662086</t>
+          <t>1664455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>525968</t>
+          <t>524766</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>616499</t>
+          <t>611561</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>875309</t>
+          <t>867949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>985535</t>
+          <t>987318</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1422095</t>
+          <t>1417794</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1562434</t>
+          <t>1563877</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>133526</t>
+          <t>144470</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108778</t>
+          <t>119441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164702</t>
+          <t>172378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125028</t>
+          <t>137402</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107531</t>
+          <t>117779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143015</t>
+          <t>158731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>258554</t>
+          <t>281872</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226672</t>
+          <t>249244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>294532</t>
+          <t>315397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>175779</t>
+          <t>193612</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152290</t>
+          <t>169282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200419</t>
+          <t>219351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>178590</t>
+          <t>198372</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159934</t>
+          <t>179667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198057</t>
+          <t>223114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>354369</t>
+          <t>391984</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>324996</t>
+          <t>360672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383670</t>
+          <t>424878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150786</t>
+          <t>163666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127007</t>
+          <t>140544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174689</t>
+          <t>190445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149446</t>
+          <t>160818</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132925</t>
+          <t>142652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169617</t>
+          <t>180305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>271990</t>
+          <t>294654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>331029</t>
+          <t>356192</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>170073</t>
+          <t>183022</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148563</t>
+          <t>161694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191841</t>
+          <t>207645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>216797</t>
+          <t>230440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198649</t>
+          <t>211635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236863</t>
+          <t>250992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>386870</t>
+          <t>413462</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356906</t>
+          <t>379792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415306</t>
+          <t>443524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>274911</t>
+          <t>298123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135830</t>
+          <t>264397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>359556</t>
+          <t>331740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>226937</t>
+          <t>256324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205143</t>
+          <t>231033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253876</t>
+          <t>282597</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>501848</t>
+          <t>554447</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>331370</t>
+          <t>511547</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>585083</t>
+          <t>599528</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>316787</t>
+          <t>357757</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172097</t>
+          <t>326142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>411981</t>
+          <t>395546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>244949</t>
+          <t>275938</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>249539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269789</t>
+          <t>305578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>561736</t>
+          <t>633696</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>366384</t>
+          <t>590442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>648604</t>
+          <t>678707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>179106</t>
+          <t>197580</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93743</t>
+          <t>169226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237298</t>
+          <t>227323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>194945</t>
+          <t>214056</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175947</t>
+          <t>191538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216224</t>
+          <t>237607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>374050</t>
+          <t>411636</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246505</t>
+          <t>377408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>439390</t>
+          <t>449933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>417508</t>
+          <t>190371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208615</t>
+          <t>167483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>771009</t>
+          <t>218824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>286008</t>
+          <t>318793</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>262950</t>
+          <t>295272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>309740</t>
+          <t>348020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>703517</t>
+          <t>509164</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>506662</t>
+          <t>471634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1194189</t>
+          <t>544161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>193967</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166696</t>
+          <t>180624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>244982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192913</t>
+          <t>187937</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97190</t>
+          <t>165921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272270</t>
+          <t>212875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>386880</t>
+          <t>402139</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252891</t>
+          <t>360706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474449</t>
+          <t>440949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>193793</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165396</t>
+          <t>197890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>220234</t>
+          <t>257361</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>168201</t>
+          <t>199880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86146</t>
+          <t>178690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227608</t>
+          <t>223478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>361994</t>
+          <t>423351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>220099</t>
+          <t>386512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>431209</t>
+          <t>462122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>168585</t>
+          <t>200364</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>175445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193744</t>
+          <t>230980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>382045</t>
+          <t>206890</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217530</t>
+          <t>185380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>641444</t>
+          <t>232119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>550630</t>
+          <t>407254</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382110</t>
+          <t>375417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>944009</t>
+          <t>441534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -11436,67 +11436,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145981</t>
+          <t>162309</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>139321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169025</t>
+          <t>187580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>23,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>215696</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>195083</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>237931</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>24,07%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>188471</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101982</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>251423</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>334452</t>
+          <t>378005</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215880</t>
+          <t>344448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392223</t>
+          <t>413251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>195367</t>
+          <t>219337</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>190463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>227263</t>
+          <t>250147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>213929</t>
+          <t>240088</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>170882</t>
+          <t>211692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244891</t>
+          <t>265067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>409296</t>
+          <t>459425</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>355904</t>
+          <t>420133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>451067</t>
+          <t>501278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239618</t>
+          <t>260500</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213457</t>
+          <t>232623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268810</t>
+          <t>293163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>292749</t>
+          <t>245693</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230254</t>
+          <t>221691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>461617</t>
+          <t>273285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>532366</t>
+          <t>506193</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>467124</t>
+          <t>466224</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>719427</t>
+          <t>547142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>288821</t>
+          <t>298244</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>258290</t>
+          <t>269366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>320102</t>
+          <t>328716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>248556</t>
+          <t>265167</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>198171</t>
+          <t>242674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>276194</t>
+          <t>289305</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>537378</t>
+          <t>563411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>526116</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>584240</t>
+          <t>605212</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>199103</t>
+          <t>208074</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174624</t>
+          <t>182396</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224364</t>
+          <t>233664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>334039</t>
+          <t>362134</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270758</t>
+          <t>335674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>370080</t>
+          <t>390485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>533142</t>
+          <t>570208</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>466604</t>
+          <t>534627</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>574401</t>
+          <t>604935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>797772</t>
+          <t>876132</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619679</t>
+          <t>812980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>884337</t>
+          <t>941783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>758807</t>
+          <t>821751</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>619932</t>
+          <t>771528</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>854698</t>
+          <t>871180</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1556578</t>
+          <t>1697883</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1358939</t>
+          <t>1623642</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1694794</t>
+          <t>1783966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>925976</t>
+          <t>1035340</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>720820</t>
+          <t>974498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1016243</t>
+          <t>1090705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>884489</t>
+          <t>919883</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>751071</t>
+          <t>870671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1044637</t>
+          <t>969905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1810465</t>
+          <t>1955223</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1569734</t>
+          <t>1869656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1987222</t>
+          <t>2031007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>787298</t>
+          <t>859854</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>626681</t>
+          <t>803685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>870604</t>
+          <t>911882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>22,86%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>974992</t>
+          <t>846931</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>798814</t>
+          <t>802007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1455734</t>
+          <t>889250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1762290</t>
+          <t>1706785</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1559234</t>
+          <t>1638263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2316422</t>
+          <t>1775771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>932665</t>
+          <t>743776</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>726198</t>
+          <t>697179</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1480569</t>
+          <t>789609</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1025315</t>
+          <t>1127063</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>833870</t>
+          <t>1081305</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1116157</t>
+          <t>1176427</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1957981</t>
+          <t>1870839</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1721211</t>
+          <t>1801687</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2611019</t>
+          <t>1939504</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
